--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_03_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_03_22_Cau.xlsx
@@ -721,7 +721,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Match ở tài liệu danh tính, không ở chunk ID duy nhất.</t>
+          <t>Trong thiết kế API quản lý vòng đời tài liệu, `delete_document(doc_id)` xóa toàn bộ các chunk thuộc về `doc_id` đó. Với `doc_id='A'`, lần gọi đầu tiên xóa toàn bộ 3 chunk A::0, A::1, A::2 và giữ lại B::0 (trả về 3); lần gọi thứ hai tài liệu A đã không còn nên trả về 0 mà không làm thay đổi kho hay báo lỗi bắt buộc.</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ một biến thay đổi và xác định rõ hành vi khi không có kết quả.</t>
+          <t>Khi cân chỉnh ngưỡng tương đồng (threshold), tăng ngưỡng làm tăng tỷ lệ rỗng (no-result) trong khi giảm ngưỡng làm tăng nhiễu. Quyết định đúng là đánh giá sự đánh đổi giữa recall và hậu quả của việc không có kết quả, từ đó chọn ngưỡng cân bằng kèm cơ chế fallback minh bạch.</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Citation không thể thay một thông tin thực không có trong ngữ cảnh.</t>
+          <t>Khi ngữ cảnh được truy xuất (retrieved context) không chứa thông tin trả lời cho câu hỏi của người dùng, hành vi tuân thủ nguyên tắc có căn cứ (groundedness) là tuyên bố rõ ràng không đủ thông tin hoặc yêu cầu người dùng làm rõ; không được bịa citation hay dùng kiến thức ngoài lề rồi gán nhãn trích dẫn giả mạo.</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một filter chỉ hữu ích nếu field phân biệt ứng viên phù hợp.</t>
+          <t>Nếu bộ lọc (filter) theo thuộc tính `department` không làm thay đổi kết quả nào trên 20 truy vấn kiểm thử do toàn bộ các bản ghi trong kho đều có cùng giá trị department, trường này không mang lại giá trị phân loại (discriminatory utility) trong tập dữ liệu; nhóm cần xem xét loại bỏ hoặc thiết kế lại cấu trúc metadata.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_03_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_07_Full_108_Cau/Day_07_Ngan_Hang_Phan_03_22_Cau.xlsx
@@ -624,10 +624,23 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Áp top-k sau khi đã xác định candidate hợp lệ.
-Phân tích theo nguyên lý thiết kế: Áp top-k sau khi đã xác định candidate hợp lệ.</t>
+- [Phân tích cơ chế Pre-filtering] (1.5 điểm): Giải thích rõ quy trình lọc ứng viên trước rồi xếp hạng, trả về đúng bản ghi Engineering (0.90).
+- [Phân tích cơ chế Post-filtering &amp; Hậu quả] (1.5 điểm): Giải thích rõ việc lấy Top-1 Marketing (0.95) rồi lọc sẽ dẫn đến kết quả rỗng [], bỏ sót tài liệu hợp lệ.
+- [Kết luận kiến trúc] (1.0 điểm): Khẳng định ưu thế tuyệt đối của Pre-filtering trong hệ thống RAG doanh nghiệp.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. So sánh chi tiết hai cơ chế lọc:
+- Lọc trước khi xếp hạng (Pre-filtering):
+  + Cơ chế: Hệ thống áp dụng bộ lọc metadata `department = 'engineering'` lên toàn bộ tập dữ liệu (hoặc sử dụng inverted index trên metadata) để lọc ra tập các ứng viên hợp lệ trước. Sau đó, thuật toán tìm kiếm vector chỉ tính toán tương đồng và xếp hạng trên tập ứng viên này để lấy `top_k = 1`.
+  + Kết quả: Kết quả Engineering tốt nhất (điểm 0.90) được trả về ở vị trí số 1. Yêu cầu của người dùng được thỏa mãn trọn vẹn.
+- Xếp hạng trước khi lọc (Post-filtering):
+  + Cơ chế: Thuật toán vector tìm kiếm `top_k = 1` trên toàn bộ kho dữ liệu trước; sau đó mới áp dụng bộ lọc `department = 'engineering'` trên danh sách kết quả trả về.
+  + Kết quả: Bước tìm kiếm vector trả về bản ghi Marketing (điểm 0.95). Bước lọc sau đó kiểm tra thấy bản ghi này không khớp phòng ban Engineering nên loại bỏ. Kết quả cuối cùng trả về danh sách rỗng `[]`, hoàn toàn bỏ lỡ bản ghi Engineering điểm 0.90!
+2. Kết luận thiết kế:
+Trong các hệ thống tìm kiếm có điều kiện ràng buộc kinh doanh nghiêm ngặt, Post-filtering cực kỳ nguy hiểm và dễ gây hiện tượng 'kết quả rỗng giả tạo' khi `k` nhỏ. Bắt buộc phải triển khai **Pre-filtering** (hoặc Single-stage Filtered Search kết hợp HNSW với payload filter như trong Qdrant/Milvus).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Post-filtering (lấy Top-K rồi mới lọc) chịu rủi ro nghiêm trọng về độ phủ vì tập Top-K ban đầu có thể bị thống trị hoàn toàn bởi các tài liệu không thỏa mãn bộ lọc. Pre-filtering đảm bảo 100% các phần tử được xếp hạng đều hợp lệ. Các vector database hiện đại sử dụng kỹ thuật Single-stage filtering (lọc trực tiếp trong quá trình duyệt đồ thị HNSW) để vừa đạt hiệu năng cao vừa bảo đảm không bao giờ bỏ sót kết quả hợp lệ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Qdrant Documentation: 'Filtering Clause &amp; Pre-filtering in Vector Search' (https://qdrant.tech/documentation/concepts/filtering/)</t>
         </is>
       </c>
     </row>
@@ -752,10 +765,27 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi experiment chỉ đổi một control rồi mới kết hợp các thay đổi.
-Phân tích theo nguyên lý thiết kế: Mỗi experiment chỉ đổi một control rồi mới kết hợp các thay đổi.</t>
+- [Nguyên tắc kiểm soát biến số] (1.0 điểm): Nêu rõ nguyên tắc cô lập từng biến số trên tập testset đóng băng.
+- [Thứ tự xử lý từng tầng lỗi] (1.5 điểm): Sắp xếp đúng trình tự logic: sửa filter semester trước, quét tối ưu k, rồi mới nới lỏng similarity threshold.
+- [Chỉ số đo lường cho từng bước] (1.5 điểm): Đưa ra metric cụ thể cho từng bước: Zero-result rate, Recall@k, Noise ratio, Context Precision.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Kế hoạch tinh chỉnh có kiểm soát (Controlled Retrieval Tuning Plan):
+Áp dụng nguyên tắc tách biệt biến số (Single-Variable Isolation): Mỗi thí nghiệm chỉ thay đổi duy nhất một tham số, đo lường trên tập kiểm thử chuẩn hóa đã đóng băng (Frozen Gold Testset) trước khi kết hợp.
+- Bước 1: Khắc phục lỗi lọc sai thời kỳ (Eligibility Filter Fix)
+  + Hành động: Sửa điều kiện lọc `semester` để không loại bỏ đáp án mới (cho phép `semester IN ('current', 'upcoming')` hoặc bỏ lọc semester tạm thời để xác lập ground-truth).
+  + Phép đo: Xác nhận 100% truy vấn có tài liệu mới không bị chặn ở tầng metadata.
+- Bước 2: Tinh chỉnh tham số Top-K (Search Depth Tuning)
+  + Hành động: Giữ cố định không dùng similarity threshold. Thử nghiệm quét giá trị `k` từ 2 đến 8 (các bước: `k = 3, 4, 5, 6`).
+  + Phép đo: Đo Recall@k (đảm bảo không bỏ sót bằng chứng thứ ba) và Noise Ratio (tỷ lệ chunk rác lọt vào context). Xác định điểm uốn tối ưu (ví dụ `k = 4` hoặc `k = 5`).
+- Bước 3: Tinh chỉnh Ngưỡng tương đồng (Similarity Threshold Tuning)
+  + Hành động: Nhận diện ngưỡng 0.85 quá chặt làm rỗng 30% truy vấn. Hạ dần ngưỡng `threshold` từ 0.85 xuống 0.75, 0.70, 0.65 với `k` tối ưu đã tìm ở Bước 2.
+  + Phép đo: Đo Zero-result Query Rate (mục tiêu &lt; 2%) kết hợp Context Precision.
+- Bước 4: Đánh giá tổng hợp và nghiệm thu (Integration Validation)
+  + Chạy toàn bộ pipeline tích hợp với bộ tham số tối ưu đã chọn, so sánh với baseline ban đầu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi hệ thống truy xuất đồng thời gặp nhiều lỗi (thiếu bằng chứng, thừa nhiễu, tỷ lệ rỗng cao do threshold chặt, filter chặn sai), việc thay đổi nhiều tham số cùng lúc sẽ dẫn đến hỗn loạn thực nghiệm và không xác định được nguyên nhân gốc rễ. Quy trình chuẩn hóa yêu cầu sửa lỗi bộ lọc điều kiện tiên quyết trước, sau đó tối ưu hóa k, và cuối cùng mới điều chỉnh ngưỡng similarity.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE: 'Controlled Experimentation and Tuning Principles' &amp; Ragas Documentation: 'Retrieval Metrics'</t>
         </is>
       </c>
     </row>
@@ -883,10 +913,25 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đừng biến tên vendor hoặc giá hiện tại thành kiến thức cố định.
-Phân tích theo nguyên lý thiết kế: Đừng biến tên vendor hoặc giá hiện tại thành kiến thức cố định.</t>
+- [Lựa chọn Managed DBaaS có căn cứ] (1.5 điểm): Chọn Managed Cloud Vector Database dựa trên đánh đổi năng lực 2 kỹ sư, yêu cầu HA/Backup cho 10M vectors.
+- [Ràng buộc độ trễ theo vùng] (1.0 điểm): Nhấn mạnh yêu cầu colocation cùng Cloud Region để đảm bảo latency thấp.
+- [Danh mục thông tin phiên bản cần kiểm tra] (1.5 điểm): Liệt kê các yếu tố kiểm tra trước: SLA, indexing metadata cost, payload size, SLA backup/restore.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn lớp triển khai (Deployment Class Selection):
+Chọn **Managed Cloud Vector Database (DBaaS)** (ví dụ: Pinecone Serverless/Standard, Qdrant Cloud Managed, hoặc AWS OpenSearch Serverless / Azure AI Search).
+Căn cứ lựa chọn:
+- Quy mô đội ngũ: Startup chỉ có 2 kỹ sư; việc tự host (self-hosted) cụm Milvus hoặc Elasticsearch phân tán đòi hỏi chi phí vận hành (ops overhead), thiết lập sharding, backup snapshot và quản lý node quá tải, vượt quá nguồn lực nhân sự.
+- Quy mô dữ liệu và độ khả dụng: 10 triệu vector đòi hỏi cụm phân tán để đảm bảo tính sẵn sàng cao (High Availability - HA) và tự động sao lưu dự phòng (Automated Backups/Disaster Recovery).
+- Độ trễ: Cần chọn nhà cung cấp có Data Plane triển khai tại cùng Region/Availability Zone với ứng dụng chính (ví dụ: `ap-southeast-1` Singapore) để đảm bảo độ trễ mạng cực thấp (&lt; 10 ms).
+2. Các thông tin phụ thuộc phiên bản cần kiểm tra trước khi quyết định:
+- Hỗ trợ lọc Metadata có chỉ mục (Indexed Metadata Filtering) và chi phí gắn kèm trên 10 triệu bản ghi.
+- Giới hạn kích thước payload/metadata trên mỗi vector và chính sách tính phí theo dung lượng lưu trữ (Storage/Read-Write Unit pricing).
+- Cơ chế High Availability và SLA cam kết thời gian hoạt động (uptime SLA &gt;= 99.9%).
+- Quy trình sao lưu định kỳ, restore point-in-time và chính sách mã hóa dữ liệu khi nghỉ (encryption at rest) đáp ứng compliance.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quyết định chọn hạ tầng cơ sở dữ liệu vector phải cân bằng giữa năng lực vận hành của đội ngũ (team operational capacity) và các ràng buộc kỹ thuật. Với đội ngũ mỏng (2 kỹ sư), giải pháp Managed Service giúp chuyển giao gánh nặng bảo trì HA/Backup sang nhà cung cấp. Các thông số phụ thuộc phiên bản về định tuyến vùng (regional latency) và cơ chế lọc metadata là yếu tố then chốt quyết định tính khả thi dài hạn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+AWS Architecture Center: 'Selecting Managed Vector Databases for Production Workloads' &amp; Pinecone Architecture Guide</t>
         </is>
       </c>
     </row>
@@ -967,10 +1012,24 @@
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đóng băng đầu ra nào ở giữa hai pha?
-Phân tích theo nguyên lý thiết kế: Đóng băng đầu ra nào ở giữa hai pha?</t>
+- [Thiết kế kích hoạt pha Offline] (1.5 điểm): Xác định đúng pha offline chỉ kích hoạt khi tài liệu thay đổi, tạo ra chỉ mục đóng băng có phiên bản.
+- [Thiết kế luồng pha Online] (1.0 điểm): Xác định pha online chỉ embed câu hỏi và tìm kiếm trên chỉ mục sẵn có.
+- [Cơ chế vô hiệu hóa Cache] (1.5 điểm): Đưa ra giải pháp gắn index version vào cache key để tự động invalidate cache cũ khi có chính sách mới.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế phân tách ranh giới Ngoại tuyến và Trực tuyến (Offline / Online Separation):
+- Pha Ngoại tuyến (Offline Ingestion Pipeline - Xử lý theo sự kiện hoặc định kỳ):
+  + Kích hoạt (Trigger): Chỉ chạy khi có sự kiện thay đổi dữ liệu nguồn (Webhook tài liệu cập nhật, CI/CD pipeline tài liệu, hoặc batch job định kỳ ban đêm). Tuyệt đối không chạy khi người dùng gửi câu hỏi!
+  + Ranh giới đầu ra đóng băng: Đầu ra của pha offline là Chỉ mục Vector có phiên bản (Versioned Vector Index, ví dụ `index_v2.1`) kèm bản đồ siêu dữ liệu (Metadata Store). Khi hoàn tất nhập liệu, hệ thống chạy kiểm thử kiểm tra tính sẵn sàng rồi chuyển cờ 'active_version' sang chỉ mục mới.
+- Pha Trực tuyến (Online Serving Pipeline - Xử lý thời gian thực per query):
+  + Kích hoạt: Người dùng gửi câu hỏi truy vấn.
+  + Luồng thực thi: Chỉ thực hiện sinh vector embedding cho chính câu hỏi (Query Embedding), áp dụng bộ lọc metadata, truy vấn Top-K trên chỉ mục vector đang hoạt động (Active Index) và đưa vào LLM để sinh câu trả lời.
+2. Xử lý bộ đệm truy vấn khi chính sách thay đổi (Cache Invalidation Strategy):
+- Cơ chế: Khi chỉ mục offline phát hành phiên bản mới, hệ thống tự động vô hiệu hóa toàn bộ cache truy vấn (Cache Invalidation) bằng cách gắn `index_version` vào khóa cache (`key = hash(query + index_version)`).
+- Kết quả: Ngăn chặn triệt để tình trạng cache query trả về kết quả thuộc chính sách cũ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một lỗi kiến trúc sơ đẳng là trộn lẫn Ingestion Pipeline vào Serving Request Path, khiến mọi câu hỏi đều phải trích xuất và embed lại toàn bộ kho tri thức, làm sập hệ thống vì độ trễ khủng khiếp. Nguyên tắc vàng của RAG là 'Embed once offline, query fast online' với cơ chế version-based cache invalidation.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Gao et al. (2023): 'Retrieval-Augmented Generation for Large Language Models: A Survey' &amp; Martin Fowler: 'Cache Invalidation Strategies'</t>
         </is>
       </c>
     </row>
@@ -1001,10 +1060,28 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một document-level field phải xuất hiện ở mọi chunk cần dùng nó.
-Phân tích theo nguyên lý thiết kế: Một document-level field phải xuất hiện ở mọi chunk cần dùng nó.</t>
+- [Đặc tả ID &amp; Metadata 3 chunk] (1.5 điểm): Thiết kế đúng định danh duy nhất (library::chunk_0, 1, 2) và sao chép đầy đủ metadata cấp tài liệu cho cả 3 chunk.
+- [Kiểm tra tính kế thừa metadata] (1.5 điểm): Nêu rõ điều kiện kiểm tra trường cấp tài liệu phải xuất hiện ở 100% các chunk con.
+- [Kiểm tra tính liên tục của index] (1.0 điểm): Kiểm tra chunk_index liên tục từ 0 đến N-1 và tính duy nhất của khóa chính.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Danh tính bản ghi (Record Identity) và Metadata cho từng chunk:
+Khi tệp có thông tin đầu tệp `{doc_id: 'library', audience: 'student', source_url: 'https://edu.vn/lib'}` tạo ra 3 chunk, metadata phải được kế thừa đầy đủ:
+- Chunk 0:
+  + `record_id`: `"library::chunk_0"`
+  + `metadata`: `{"doc_id": "library", "audience": "student", "source_url": "https://edu.vn/lib", "chunk_index": 0, "total_chunks": 3}`
+- Chunk 1:
+  + `record_id`: `"library::chunk_1"`
+  + `metadata`: `{"doc_id": "library", "audience": "student", "source_url": "https://edu.vn/lib", "chunk_index": 1, "total_chunks": 3}`
+- Chunk 2:
+  + `record_id`: `"library::chunk_2"`
+  + `metadata`: `{"doc_id": "library", "audience": "student", "source_url": "https://edu.vn/lib", "chunk_index": 2, "total_chunks": 3}`
+2. Điều kiện kiểm tra tính toàn vẹn (Verification Invariants):
+- Điều kiện 1 (Document-level Metadata Propagation): Mọi chunk con đều phải chứa 100% các trường cấp tài liệu (`doc_id`, `audience`, `source_url`) trùng khớp với tài liệu gốc.
+- Điều kiện 2 (Chunk-level Uniqueness &amp; Sequence): Mỗi chunk phải có `record_id` duy nhất dạng `{doc_id}::chunk_{index}` và `chunk_index` phải là dãy số liên tục từ `0` đến `total_chunks - 1`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Quá trình phân đoạn (chunking) phá vỡ tài liệu lớn thành các đoạn nhỏ nhưng không được làm thất thoát ngữ cảnh cấp tài liệu. Kỹ thuật Metadata Propagation đảm bảo mọi chunk con đều mang đầy đủ thuộc tính phân quyền (`audience`) và nguồn gốc (`source_url`), giúp các bộ lọc metadata hoạt động chính xác trên từng đơn vị tìm kiếm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LlamaIndex Documentation: 'Metadata Extraction and Ingestion Pipeline' (https://docs.llamaindex.ai/en/stable/module_guides/loading/ingestion_pipeline/)</t>
         </is>
       </c>
     </row>
@@ -1084,10 +1161,26 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một record trả lời “thế giới nói gì”; record kia trả lời “người dùng này đang ở trạng thái nào”.
-Phân tích theo nguyên lý thiết kế: Một record trả lời “thế giới nói gì”; record kia trả lời “người dùng này đang ở trạng thái nào”.</t>
+- [Tách biệt quy ước đọc/cập nhật] (1.5 điểm): Phân định rõ kho tri thức toàn cục (quản trị viên cập nhật, công khai) và bộ nhớ cá nhân (user_id riêng, cập nhật theo phiên, TTL).
+- [Rủi ro rò rỉ quyền riêng tư] (1.5 điểm): Phân tích rủi ro nghiêm trọng khi ghi chú nhạy cảm cá nhân bị trả về cho người khác khi query chung.
+- [Rủi ro sai lệch nghiệp vụ] (1.0 điểm): Nêu rủi ro ô nhiễm context khiến câu trả lời chính sách bị thiên vị hoặc sai lệch.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tách quy ước đọc và cập nhật (Separation of Contracts):
+- Kho Tri thức Chính sách (Policy Knowledge Base):
+  + Bản chất: Tri thức khách quan toàn cục (Global Objective Knowledge) mô tả quy định tổ chức.
+  + Quy ước đọc: Được truy cập bởi mọi người dùng; hỗ trợ tìm kiếm ngữ nghĩa kèm metadata filter (khoa, phiên bản).
+  + Quy ước cập nhật: Chỉ do Quản trị viên/Phòng ban chức năng cập nhật qua Ingestion Pipeline có kiểm duyệt.
+- Kho Bộ nhớ Người dùng (User Ephemeral / Personal Memory):
+  + Bản chất: Trạng thái chủ quan cá nhân (Personal Context / Affective State) mô tả hồ sơ hoặc cảm xúc người học.
+  + Quy ước đọc: Được phân vùng nghiêm ngặt theo `user_id` (chỉ truy xuất khi xác thực đúng phiên của Lan).
+  + Quy ước cập nhật: Tự động cập nhật theo thời gian thực từ các lượt tương tác của người dùng, có cơ chế hết hạn (TTL/expiry).
+2. Rủi ro nghiêm trọng nếu truy vấn chung (Risks of Unified Querying):
+- Rò rỉ thông tin riêng tư (PII / Privacy Leakage): Trạng thái cá nhân nhạy cảm của Lan ('đang stress') có thể bị trả về cho người dùng khác nếu câu hỏi của họ tương đồng về ngữ nghĩa với đoạn ghi chú này.
+- Ô nhiễm ngữ cảnh chính sách (Context Pollution): Khi hỏi về quy chế học vụ, việc nhầm lẫn giữa quy định chung và ghi chú tâm lý cá nhân sẽ khiến LLM đưa ra câu trả lời thiên vị hoặc sai lệch quy định đào tạo.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong hệ thống tác tử thông minh, việc nhầm lẫn giữa Bộ nhớ ngữ cảnh người dùng (User Memory) và Cơ sở tri thức (Domain Knowledge) là một lỗ hổng nghiêm trọng về quyền riêng tư và an toàn thông tin. Chúng phải được lưu trữ trong các Collection hoặc Namespace độc lập với các chính sách phân quyền truy cập (Access Control Lists) khác nhau.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Agent Memory vs. Vector Store Retrievers' &amp; OWASP LLM06: Sensitive Information Disclosure</t>
         </is>
       </c>
     </row>
@@ -1118,10 +1211,23 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Điểm truy xuất không thay thế điều kiện đủ dùng/nguồn chính.
-Phân tích theo nguyên lý thiết kế: Điểm truy xuất không thay thế điều kiện đủ dùng/nguồn chính.</t>
+- [Lọc ngữ cảnh theo độ tin cậy] (1.5 điểm): Giữ lại duy nhất C1 (chính sách hiện hành), loại bỏ dứt khoát C2 (blog không nguồn) và C3 (chính sách cũ).
+- [Đặc tả Answer Contract] (1.5 điểm): Thiết lập ràng buộc trích dẫn nguồn cụ thể [Doc 1] cho mọi khẳng định.
+- [Quy tắc từ chối khi thiếu bằng chứng] (1.0 điểm): Nêu rõ cơ chế từ chối trả lời (abstention) nếu C1 không chứa thông tin, cấm bịa đặt.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế cách chọn ngữ cảnh (Context Selection &amp; Filtering Protocol):
+- Phân loại độ tin cậy và hiệu lực nguồn (Source Authority Filtering):
+  + C1 (Chính sách hiện hành): Nguồn thẩm quyền cao nhất (Primary Ground-Truth), thỏa mãn metadata `is_active: true`, được giữ lại làm ngữ cảnh cốt lõi.
+  + C2 (Blog không nguồn): Nguồn không có thẩm quyền (Unverified Secondary Source), tiềm ẩn thông tin sai lệch; bị loại bỏ hoàn toàn khỏi context prompt.
+  + C3 (Chính sách cũ): Đã hết hiệu lực (`is_active: false`); bị loại bỏ để tránh gây mâu thuẫn thông tin và ảo giác.
+- Ngữ cảnh cuối cùng đưa vào Prompt: Chỉ chứa duy nhất C1 kèm định danh trích dẫn `[Doc 1: Policy v3]`. Tuyệt đối không đưa C2 và C3 vào prompt.
+2. Hợp đồng câu trả lời có căn cứ (Answer Contract):
+- System Prompt Constraint: Yêu cầu mô hình chỉ trả lời dựa trên bằng chứng được cung cấp trong ngữ cảnh đã duyệt. Mọi mốc thời gian/deadline phải đi kèm trích dẫn chính xác `[Doc 1]`.
+- Quy tắc từ chối (Abstention Rule): Nếu ngữ cảnh hợp lệ (C1) không chứa thông tin về deadline mới được hỏi, mô hình bắt buộc phải trả lời: 'Tài liệu chính sách hiện hành không có thông tin về thời hạn này', tuyệt đối không được suy diễn từ kiến thức chung bên ngoài.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hệ thống RAG tin cậy phải thực hiện thanh lọc ngữ cảnh (Context Curation) trước khi đưa vào mô hình tạo sinh. Điểm tương đồng vector cao không đồng nghĩa với nguồn tin cậy. Việc loại bỏ các nguồn không chính thức và chính sách hết hạn là tuyến phòng thủ then chốt để chống ảo giác và câu trả lời sai lệch.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Lewis et al. (2020): 'Retrieval-Augmented Generation for Knowledge-Intensive NLP Tasks' &amp; Anthropic Claude Prompt Engineering Guide</t>
         </is>
       </c>
     </row>
@@ -1197,10 +1303,33 @@
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi gold phải chỉ về nguồn cụ thể trước experiment.
-Phân tích theo nguyên lý thiết kế: Mỗi gold phải chỉ về nguồn cụ thể trước experiment.</t>
+- [Thiết kế 3 dòng testset đầy đủ] (1.5 điểm): Xây dựng 3 dòng kiểm thử rõ ràng với câu hỏi thực tế, trong đó có 1 dòng phụ thuộc metadata (audience=staff/student).
+- [Xác định rõ ràng Gold Chunks &amp; Ground Truth] (1.5 điểm): Cung cấp expected_doc_ids cụ thể và câu trả lời chuẩn xác thực từ nguồn.
+- [Quy tắc đóng băng nghiêm ngặt] (1.0 điểm): Nêu rõ quy tắc khóa dữ liệu trước thử nghiệm và cấm sửa đổi sau khi thấy kết quả.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế 3 dòng dữ liệu kiểm thử chuẩn (Benchmark Gold Dataset):
+- Dòng 1 (Sinh viên tra cứu học vụ):
+  + `query`: 'Thời hạn sinh viên nộp đơn hoãn thi kết thúc học phần là khi nào?'
+  + `filter_criteria`: `{"audience": "student", "department": "academic"}`
+  + `expected_doc_ids`: `["academic_policy_2026::chunk_12"]`
+  + `gold_answer`: 'Sinh viên phải nộp đơn trước ngày thi ít nhất 03 ngày làm việc kèm minh chứng hợp lệ.'
+- Dòng 2 (Cán bộ/Giảng viên tra cứu chế độ - Phụ thuộc Metadata):
+  + `query`: 'Quy định định mức giờ nghiên cứu khoa học bắt buộc đối với giảng viên cơ hữu.'
+  + `filter_criteria`: `{"audience": "staff", "role": "faculty"}`
+  + `expected_doc_ids`: `["staff_handbook_v4::chunk_45"]`
+  + `gold_answer`: 'Giảng viên cơ hữu phải hoàn thành tối thiểu 600 giờ chuẩn nghiên cứu khoa học trong năm học.'
+- Dòng 3 (Đăng ký môn học - Trường hợp ngoại lệ):
+  + `query`: 'Điều kiện đăng ký môn học vượt số tín chỉ tối đa trong một học kỳ.'
+  + `filter_criteria`: `{"audience": "student", "category": "course_registration"}`
+  + `expected_doc_ids`: `["registration_rules::chunk_08"]`
+  + `gold_answer`: 'Chỉ sinh viên có GPA tích lũy &gt;= 3.2 mới được đăng ký tối đa 24 tín chỉ khi có phê duyệt của Trưởng khoa.'
+2. Quy tắc đóng băng bộ dữ liệu (Freezing Rules):
+- Bộ kiểm thử (câu hỏi, filter, gold chunks, gold answer) phải được phiên bản hóa và khóa chặt (frozen) trước khi thực hiện bất kỳ thử nghiệm thuật toán nào.
+- Tuyệt đối không được chỉnh sửa câu hỏi hoặc thêm bớt expected chunks sau khi quan sát kết quả của một chiến lược cụ thể nhằm tránh rò rỉ dữ liệu (benchmark contamination/overfitting).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Benchmark retrieval chuẩn phải gắn liền với thực tế nghiệp vụ và bao quát cả tìm kiếm ngữ nghĩa lẫn lọc thuộc tính metadata. Quy tắc đóng băng bộ dữ liệu (Dataset Freezing) là nguyên tắc cốt lõi của phương pháp luận khoa học, ngăn ngừa hiện tượng thiên vị thực nghiệm hoặc 'chữa đề theo kết quả'.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Es et al. (2023): 'Ragas: Automated Evaluation of Retrieval Augmented Generation' &amp; TREC Benchmark Guidelines</t>
         </is>
       </c>
     </row>
@@ -1231,10 +1360,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: MRR chỉ nhìn rank của relevant đầu tiên.
-Phân tích theo nguyên lý thiết kế: MRR chỉ nhìn rank của relevant đầu tiên.</t>
+- [Tính đúng Precision@5] (1.0 điểm): Tính chính xác 2/5 = 0.40 (40%).
+- [Tính đúng Recall@5] (1.0 điểm): Tính chính xác 2/4 = 0.50 (50%).
+- [Tính đúng MRR] (1.0 điểm): Tính chính xác RR = 1/1 = 1.0 (100%).
+- [Diễn giải ý nghĩa nhiễu &amp; bỏ sót] (1.0 điểm): Phân tích sâu sắc: 60% kết quả là nhiễu và bỏ sót 50% tài liệu liên quan trong kho.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính toán các chỉ số xếp hạng truy xuất (Retrieval Metrics Computation):
+Theo đề bài: Danh sách Top-5 có nhãn liên quan là `[1, 0, 1, 0, 0]`. Tổng số tài liệu liên quan trong toàn bộ kho tài liệu là `N_rel = 4`.
+- **Precision@5**:
+  `Precision@5 = (Số tài liệu liên quan trong Top-5) / 5 = 2 / 5 = 0.40` (hoặc 40%).
+- **Recall@5**:
+  `Recall@5 = (Số tài liệu liên quan trong Top-5) / (Tổng số tài liệu liên quan trong kho) = 2 / 4 = 0.50` (hoặc 50%).
+- **MRR (Mean Reciprocal Rank)**:
+  Vị trí đầu tiên xuất hiện tài liệu liên quan (first relevant rank) là vị trí 1 (`rank = 1`).
+  `RR = 1 / 1 = 1.0` (hoặc 100%).
+2. Diễn giải kết quả phân tích:
+- Dấu hiệu kết quả nhiễu: Precision@5 chỉ đạt 0.40 (có tới 3 trên 5 chunk ở các vị trí 2, 4, 5 là hoàn toàn không liên quan). Điều này cho thấy tập kết quả chứa 60% nhiễu, làm lãng phí context window của LLM và tăng nguy cơ gây ảo giác.
+- Dấu hiệu mục tiêu bị bỏ sót: Recall@5 chỉ đạt 0.50, chứng minh hệ thống đã bỏ sót một nửa số tài liệu liên quan trong kho (2/4 tài liệu liên quan không lọt vào Top-5).
+- Điểm tích cực: MRR = 1.0 cho thấy hệ thống rất xuất sắc trong việc đưa ngay một tài liệu liên quan lên vị trí cao nhất (hạng 1).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Các chỉ số đánh giá truy xuất phản ánh các khía cạnh khác nhau: Precision@K đo mật độ thông tin hữu ích trong vùng ngữ cảnh; Recall@K đo độ bao phủ toàn diện của bằng chứng; MRR đo tốc độ tiếp cận tài liệu đúng đầu tiên. Một hệ thống có MRR cao nhưng Precision thấp vẫn gây rủi ro lớn cho mô hình tạo sinh do lượng nhiễu trong context quá cao.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Manning, Raghavan &amp; Schütze: 'Introduction to Information Retrieval' (Cambridge University Press) - Chapter 8: Evaluation in information retrieval</t>
         </is>
       </c>
     </row>
@@ -1315,10 +1462,25 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi defect cần một boundary-level repair riêng.
-Phân tích theo nguyên lý thiết kế: Mỗi defect cần một boundary-level repair riêng.</t>
+- [Đánh giá chính xác lỗi của Chunk A và B] (1.5 điểm): Chỉ ra lỗi đứt gãy mệnh đề ở Chunk A và mất ngữ cảnh dẫn nhập/điều kiện ở Chunk B.
+- [Đánh giá chính xác lỗi của Chunk C] (1.0 điểm): Nhận diện lỗi ô nhiễm ngữ cảnh chéo do gộp 2 chính sách không liên quan.
+- [Đề xuất sửa theo đúng tầng kiến trúc] (1.5 điểm): Đưa ra giải pháp chuẩn: Sentence-boundary/Parent-document cho A-B và Markdown heading splitting cho C.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chấm điểm tính mạch lạc của từng chunk (Coherence &amp; Boundary Assessment):
+- **Chunk A** (Kết thúc bằng 'Được hoàn phí nếu...'): Điểm kém / Lỗi đứt gãy biên ngữ nghĩa (Dangling Clause Defect). Mệnh đề điều kiện bị cắt cụt ở cuối, không cung cấp được điều kiện cụ thể để được hoàn tiền.
+- **Chunk B** (Bắt đầu bằng mức tiền nhưng thiếu điều kiện): Điểm kém / Lỗi mất ngữ cảnh dẫn nhập (Missing Antecedent Defect). Nêu con số tiền tệ nhưng không biết áp dụng cho trường hợp nào, gây rủi ro hiểu sai lệch chính sách.
+- **Chunk C** (Chứa hai chính sách không liên quan): Điểm kém / Lỗi ô nhiễm ngữ cảnh chéo (Cross-Topic Contamination Defect). Gộp hai chủ đề độc lập vào một chunk làm loãng vector embedding và gây nhiễu cho bước tạo sinh.
+2. Đề xuất sửa chữa theo đúng tầng kiến trúc (Layer-wise Repair Proposal):
+- Sửa chữa tầng Phân đoạn (Chunking Boundary Repair) cho Chunk A và B:
+  + Chuyển từ Fixed-length Chunking sang Sentence-boundary Chunking hoặc Recursive Character Splitting có phân tách theo dấu câu (`. `, `
+`).
+  + Áp dụng `chunk_overlap` từ 40-80 ký tự hoặc dùng Parent-Document Retriever để khi tìm thấy mệnh đề con, toàn bộ đoạn văn bản đầy đủ chứa cả điều kiện và mức tiền sẽ được đưa vào context.
+- Sửa chữa tầng Cấu trúc tài liệu (Document Structure Parsing) cho Chunk C:
+  + Bổ sung bước phân tách theo cấu trúc tiêu đề (Markdown Heading Splitter) trước khi chunking để mỗi chính sách nằm trong một ranh giới độc lập, không bị gộp chung.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tính mạch lạc của chunk (Chunk Coherence) ảnh hưởng trực tiếp đến chất lượng embedding và khả năng suy luận của LLM. Các lỗi cắt ngang câu (broken syntax) và trộn lẫn chủ đề (topic contamination) phải được khắc phục tận gốc ở tầng tiền xử lý tài liệu và chiến lược phân đoạn, thay vì cố gắng xử lý bằng prompt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+LangChain Documentation: 'Text Splitters &amp; Semantic Chunker' &amp; LlamaIndex Document Processing Guide</t>
         </is>
       </c>
     </row>
@@ -1349,10 +1511,22 @@
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tách lỗi của filter logic khỏi lỗi metadata độ bao phủ.
-Phân tích theo nguyên lý thiết kế: Tách lỗi của filter logic khỏi lỗi metadata độ bao phủ.</t>
+- [Đánh giá Utility của bộ lọc] (1.5 điểm): Chỉ ra bộ lọc tăng Precision@3 lên 3/3 nhưng làm giảm Recall do loại bỏ chính sách thiếu thẻ.
+- [Tách biệt tầng lỗi] (1.0 điểm): Phân định dứt khoát lỗi thuộc về tầng chất lượng dữ liệu (metadata coverage) chứ không phải lỗi logic của bộ lọc.
+- [Kế hoạch hành động cụ thể] (1.5 điểm): Đưa ra 2 bước xử lý chuẩn xác: Backfill/chuẩn hóa dữ liệu nguồn và áp dụng điều kiện lọc an toàn tạm thời (OR audience IS NULL).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá tính hữu dụng của bộ lọc (Metadata Filter Utility Assessment):
+- Hiệu quả tăng độ chính xác (Precision Gain): Bộ lọc `audience=student` đã nâng số lượng bản ghi liên quan trong top-3 từ 2 lên 3 bản ghi (tăng Precision@3 từ 66.7% lên 100% đối với các tài liệu có gắn thẻ). Bộ lọc hoạt động hoàn hảo về mặt logic phân loại.
+- Tổn hại về độ bao phủ (Recall Trade-off / False Negative): Bộ lọc vô tình loại bỏ một chính sách đúng và có giá trị cao chỉ vì bản ghi đó bị khuyết thiếu trường metadata `audience` (Missing Metadata Defect).
+2. Phân định ranh giới lỗi:
+Cần tách bạch rõ ràng: Logic lọc của truy vấn là hoàn toàn đúng đắn; lỗi cốt lõi nằm ở **tầng chất lượng dữ liệu và độ bao phủ metadata (Data Ingestion Coverage Defect)** chứ không phải lỗi của thuật toán lọc.
+3. Quyết định bước xử lý tiếp theo:
+- Bước 1 (Sửa dữ liệu nguồn): Chạy pipeline kiểm tra và điền bù metadata (Metadata Backfill &amp; Imputation) cho toàn bộ các bản ghi bị thiếu trường `audience` trong kho dữ liệu.
+- Bước 2 (Chính sách lọc an toàn tạm thời): Trong khi chờ dữ liệu được làm sạch hoàn toàn, triển khai logic lọc nới lỏng: `WHERE audience = 'student' OR audience IS NULL` hoặc gán nhãn mặc định `audience='all'` cho các tài liệu công khai.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một bộ lọc metadata chỉ có thể phát huy tối đa giá trị khi tỷ lệ bao phủ của metadata đạt 100%. Lỗi thiếu metadata (Missing Tagging) trong quá trình nạp dữ liệu sẽ biến một bộ lọc đúng thành nguyên nhân gây đứt gãy thông tin (False Negatives). Cần phân biệt rõ lỗi logic của bộ lọc với lỗi chất lượng của dữ liệu đầu vào.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Pinecone Documentation: 'Metadata Filtering Best Practices &amp; Null Value Handling' (https://docs.pinecone.io/guides/data/filter-by-metadata)</t>
         </is>
       </c>
     </row>
@@ -1431,10 +1605,23 @@
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Theo gold fact từ source tới extracted corpus trước khi nhìn model.
-Phân tích theo nguyên lý thiết kế: Theo gold fact từ source tới extracted corpus trước khi nhìn model.</t>
+- [Xác định đúng lỗi sớm nhất] (1.5 điểm): Xác định chính xác lỗi nằm ở Tầng Trích xuất Tài liệu (Document Parser làm mất bảng), không đổ lỗi cho Generator.
+- [Phương án kỹ thuật thay thế] (1.5 điểm): Đề xuất sử dụng Layout-aware parser / Table extractor xuất ra bảng Markdown/HTML bảo toàn cấu trúc.
+- [Quy trình Rerun &amp; Kiểm tra] (1.0 điểm): Mô tả rõ quy trình chạy lại từ trích xuất, re-index đến kiểm tra xác minh câu trả lời của mô hình.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định lỗi sớm nhất trong chuỗi xử lý (Earliest Defect Localization):
+- Lỗi sớm nhất nằm ở **Tầng Trích xuất Dữ liệu (Document Extraction Layer)**.
+- Cụ thể: Bộ trích xuất văn bản (Text Parser / PDF Extractor) đã làm mất hoàn toàn bảng dữ liệu chứa câu trả lời chuẩn (Gold Answer). Các tầng phía sau (Chunking, Embedding, Vector Search, Generator) hoạt động hoàn toàn bình thường dựa trên dữ liệu đã nhận, nhưng vì dữ liệu đầu vào đã bị rỗng phần bảng nên việc Generator trả 'không có thông tin' là phản ứng hoàn toàn chính xác.
+2. Phương án thay thế kỹ thuật (Alternative Extraction Strategy):
+- Thay thế bộ parser văn bản thô bằng Bộ trích xuất nhận biết bố cục và bảng biểu chuyên dụng (Layout-Aware / Table-Aware Parser, ví dụ: Unstructured.io với mô hình `hi_res`, Azure Document Intelligence Layout API, Camelot, hoặc pdfplumber).
+- Trích xuất bảng thành định dạng có cấu trúc giữ nguyên mối liên hệ hàng - cột (Markdown Table, HTML Table hoặc cấu trúc JSON key-value) kèm tiêu đề ngữ cảnh của bảng.
+3. Quy trình chạy lại và xác minh (Rerun &amp; Verification Workflow):
+- Chạy lại trích xuất văn bản cho tài liệu nguồn với parser mới -&gt; Kiểm tra trực quan xem bảng dữ liệu đã có trong văn bản sau trích xuất chưa.
+- Re-chunk và Re-embed tài liệu vào Vector Store -&gt; Thực hiện lại truy vấn tìm kiếm và kiểm tra xem đoạn ngữ cảnh chứa bảng có lọt vào Top-K và LLM có trả lời chính xác dữ kiện chuẩn hay không.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc 'Garbage In, Garbage Out' trong RAG: nếu thông tin bị thất thoát ngay từ bước trích xuất ban đầu, không có bất kỳ kỹ thuật prompt engineering hay mô hình LLM tiên tiến nào có thể phục hồi được thông tin đó. Việc chẩn đoán lỗi phải lần ngược từ nguồn qua từng artifact trung gian để định vị chính xác mắt xích đứt gãy sớm nhất.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Unstructured Documentation: 'Extracting Tables from PDF Documents' &amp; LlamaIndex 'PDF Table Extraction Guides'</t>
         </is>
       </c>
     </row>
@@ -1465,10 +1652,20 @@
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Nếu unfiltered result đã đúng, failure nằm ở eligibility control.
-Phân tích theo nguyên lý thiết kế: Nếu unfiltered result đã đúng, failure nằm ở eligibility control.</t>
+- [Chẩn đoán chính xác nguyên nhân] (1.5 điểm): Chỉ ra việc gán cứng sai tham số lọc semester=2025 đã triệt tiêu bản ghi đúng có semester=2026.
+- [Chứng minh tầng retrieval hoạt động tốt] (1.0 điểm): Khẳng định tầng embedding và vector search đúng vì unfiltered đạt hạng 1.
+- [Cách sửa tối thiểu &amp; Phép kiểm tra] (1.5 điểm): Đưa ra cách sửa đúng tham số semester=2026 và viết test kiểm tra mapping tham số từ session.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán nguyên nhân lỗi (Root Cause Diagnosis):
+- Kết quả chạy không lọc đưa bản ghi đáp án chuẩn lên hạng 1 chứng minh rằng: Mô hình embedding, chiến lược chunking và thuật toán tìm kiếm vector hoạt động hoàn toàn chính xác về mặt ngữ nghĩa.
+- Lỗi xảy ra hoàn toàn do **Cấu hình sai điều kiện lọc thẩm quyền (Eligibility Filter Misconfiguration)**: Người truy vấn muốn tìm chính sách cho học viên kỳ `semester=2026`, nhưng tham số gửi vào bộ lọc metadata lại bị gán cứng là `semester=2025` (`department=engineering, semester=2025`). Vì bản ghi đúng có `semester=2026`, bộ lọc tiền truy vấn (pre-filter) đã loại bỏ bản ghi này ngay từ bước sàng lọc, dẫn đến kết quả trả về bị rỗng.
+2. Phép kiểm tra hoặc cách sửa tối thiểu (Minimal Fix &amp; Verification Test):
+- Cách sửa tối thiểu trong mã nguồn/API: Cập nhật tham số truy vấn của bộ lọc để lấy động từ ngữ cảnh phiên của người dùng hoặc cho phép giá trị khớp với kỳ yêu cầu: `filter = {"department": "engineering", "semester": "2026"}`.
+- Phép kiểm tra hồi quy (Regression Test): Thiết lập bài kiểm thử tự động (Unit Test / Integration Test) xác nhận rằng tham số lọc `semester` trong query payload luôn được ánh xạ tự động từ thuộc tính học kỳ hiện tại của sinh viên (`user_session.target_semester`), không bị hardcode giá trị quá khứ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi việc tìm kiếm không lọc (unfiltered retrieval) cho kết quả hoàn hảo nhưng tìm kiếm có lọc lại trả về rỗng, lỗi 100% thuộc về tầng điều phối bộ lọc (Eligibility / Metadata Filter Layer). Cần kiểm tra mapping giữa biến môi trường/người dùng và tham số query payload.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Qdrant Documentation: 'Payload Based Filtering &amp; Debugging Empty Search Results' (https://qdrant.tech/documentation/)</t>
         </is>
       </c>
     </row>
